--- a/hpi_scraper/JobsHiring/theirstack/theirstack_data.xlsx
+++ b/hpi_scraper/JobsHiring/theirstack/theirstack_data.xlsx
@@ -445,13 +445,13 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="39" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
@@ -506,47 +506,47 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>920</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>606</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>eng: 5; design: 4; it: 1; sales: 1; ops: 1</t>
+          <t>eng: 1; design: 0; it: 3; sales: 0; ops: 0</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Singapore; Kuala Lumpur, Federal Territory of Kuala Lumpur</t>
+          <t>Singapore; Jakarta</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/jobs/view/ai-ux-manager-%23aida-at-singtel-4364289550; https://sg.linkedin.com/jobs/view/network-engineer-networks-at-singtel-4371030575; https://my.linkedin.com/jobs/view/sales-commission-executive-at-singtel-4380327338; https://sg.linkedin.com/jobs/view/senior-ai-solution-designer-%23aida-at-singtel-4342970595; https://sg.linkedin.com/jobs/view/senior-solution-designer-at-singtel-4411744202; https://sg.linkedin.com/jobs/view/cybersecurity-operations-engineer-at-singtel-4381198354; https://my.linkedin.com/jobs/view/senior-engineer-compute-services-virtualization-at-singtel-4364092261; https://sg.linkedin.com/jobs/view/support-engineer-at-singtel-4411427741; https://my.linkedin.com/jobs/view/senior-solution-designer-oss-bss-at-singtel-4369396109; https://sg.linkedin.com/jobs/view/support-engineer-kubernetes-at-singtel-4411420786</t>
+          <t>https://sg.linkedin.com/jobs/view/hr-intern-6-months-at-sea-4429397962; https://sg.linkedin.com/jobs/view/associate-senior-associate-employee-engagement-at-sea-4380365310; https://id.linkedin.com/jobs/view/senior-back-end-engineer-enterprise-efficiency-sea-labs-at-sea-4261955005; https://sg.linkedin.com/jobs/view/travel-systems-partnerships-lead-at-sea-4420242659; https://id.linkedin.com/jobs/view/labs-bootcamp-program-at-sea-3740022960; https://sg.linkedin.com/jobs/view/governance-process-optimisation-lead-infrastructure-at-sea-4420241679; https://sg.linkedin.com/jobs/view/industrial-postgraduate-programme-ipp-at-sea-4224374943; https://sg.linkedin.com/jobs/view/assistant-manager-cco-s-office-at-sea-4402253763; https://au.seek.com/job/92782539?tracking=SHR-WEB-SharedJob-anz-1; https://sg.linkedin.com/jobs/view/information-technology-analyst-contract-at-sea-4419028097</t>
         </is>
       </c>
     </row>
